--- a/src/main/resources/TestData.xlsx
+++ b/src/main/resources/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akgupta\Desktop\workspace\SampleFramework\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A4A71A-C471-415C-BC68-C01FF9B27A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D72A40-036F-408A-8C69-C3F1F24D1979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2AFC021D-A9EF-4E62-A66C-A222594E6A9A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -47,19 +47,19 @@
     <t>password</t>
   </si>
   <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>problem_user</t>
+  </si>
+  <si>
+    <t>Username successfull get</t>
+  </si>
+  <si>
+    <t>password successfull get</t>
+  </si>
+  <si>
     <t>standard_user</t>
-  </si>
-  <si>
-    <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>problem_user</t>
-  </si>
-  <si>
-    <t>Username successfull get</t>
-  </si>
-  <si>
-    <t>password successfull get</t>
   </si>
 </sst>
 </file>
@@ -449,25 +449,25 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>2</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s" s="0">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
